--- a/threagile/output/vast/risks.xlsx
+++ b/threagile/output/vast/risks.xlsx
@@ -19,64 +19,64 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
     <t>CWE</t>
   </si>
   <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
     <t>Identified Risk</t>
   </si>
   <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Ticket</t>
   </si>
   <si>
     <t>Impact</t>
   </si>
   <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Check</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
     <t>Function</t>
   </si>
   <si>
     <t>Risk Category</t>
   </si>
   <si>
-    <t>Technical Asset</t>
-  </si>
-  <si>
     <t>Action</t>
-  </si>
-  <si>
-    <t>Severity</t>
   </si>
   <si>
     <t>Elevated</t>
@@ -879,64 +879,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="M1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="N1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="24" t="s">
+      <c r="O1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="24" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2">

--- a/threagile/output/vast/risks.xlsx
+++ b/threagile/output/vast/risks.xlsx
@@ -10,14 +10,20 @@
     <sheet name="VaultNote Threat Model" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$12</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'VaultNote Threat Model'!$A$1:$T$11</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
   <si>
     <t>Date</t>
   </si>
@@ -25,60 +31,54 @@
     <t>Checked by</t>
   </si>
   <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
     <t>STRIDE</t>
   </si>
   <si>
     <t>Likelihood</t>
   </si>
   <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
     <t>CWE</t>
   </si>
   <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
     <t>Mitigation</t>
   </si>
   <si>
-    <t>Check</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Severity</t>
+    <t>Ticket</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Risk Category</t>
   </si>
   <si>
     <t>Technical Asset</t>
   </si>
   <si>
-    <t>Identified Risk</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>Ticket</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
     <t>Elevated</t>
   </si>
   <si>
@@ -106,7 +106,7 @@
     <t/>
   </si>
   <si>
-    <t>82</t>
+    <t>44</t>
   </si>
   <si>
     <t>Cross-Process Credential Exposure: API Server bridges business process contexts while handling strictly-confidential data</t>
@@ -145,7 +145,7 @@
     <t>PostgreSQL Database</t>
   </si>
   <si>
-    <t>100</t>
+    <t>54</t>
   </si>
   <si>
     <t>Cross-Process Credential Exposure: PostgreSQL Database bridges business process contexts while handling strictly-confidential data</t>
@@ -210,7 +210,7 @@
     <t>Redis Cache</t>
   </si>
   <si>
-    <t>40</t>
+    <t>22</t>
   </si>
   <si>
     <t>No Redundancy for Critical Process: Redis Cache supports a critical business process without redundancy</t>
@@ -232,7 +232,7 @@
     <t>Operational Threat - Critical Business Process Without Operational Monitoring</t>
   </si>
   <si>
-    <t>Unmonitored Critical Process: API Server supports a critical business process but has no audit-logged ingress</t>
+    <t>Unmonitored Critical Process: PostgreSQL Database supports a critical business process but has no audit-logged ingress</t>
   </si>
   <si>
     <t>Enable audit logging on all assets supporting critical business processes</t>
@@ -246,24 +246,14 @@
 </t>
   </si>
   <si>
-    <t>operational-unmonitored-critical-process@api-server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application-level metrics (request rate, error rate, p99 latency) are exposed via /metrics endpoint but Prometheus scraping is not configured in the demo environment. Production monitoring stack is tracked in VAULT-123.
+    <t>operational-unmonitored-critical-process@postgresql-db</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PostgreSQL slow-query log and pg_stat_statements are enabled in the demo config. Full APM integration (Prometheus postgres_exporter + Grafana) is planned for production. Alert thresholds are being defined.
 </t>
   </si>
   <si>
     <t>VAULT-123</t>
-  </si>
-  <si>
-    <t>Unmonitored Critical Process: PostgreSQL Database supports a critical business process but has no audit-logged ingress</t>
-  </si>
-  <si>
-    <t>operational-unmonitored-critical-process@postgresql-db</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PostgreSQL slow-query log and pg_stat_statements are enabled in the demo config. Full APM integration (Prometheus postgres_exporter + Grafana) is planned for production. Alert thresholds are being defined.
-</t>
   </si>
   <si>
     <t>Unmonitored Critical Process: Redis Cache supports a critical business process but has no audit-logged ingress</t>
@@ -882,58 +872,58 @@
         <v>11</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>16</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>18</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="24" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>7</v>
-      </c>
       <c r="N1" s="24" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O1" s="24" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P1" s="24" t="s">
         <v>10</v>
       </c>
       <c r="Q1" s="24" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R1" s="24" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S1" s="24" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T1" s="24" t="s">
         <v>15</v>
@@ -1272,13 +1262,13 @@
         <v>67</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K7" s="19" t="s">
         <v>68</v>
@@ -1334,13 +1324,13 @@
         <v>67</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="K8" s="19" t="s">
         <v>75</v>
@@ -1384,55 +1374,55 @@
         <v>22</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M9" s="23" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="N9" s="23" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="R9" s="17" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="S9" s="17" t="s">
         <v>55</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1446,55 +1436,55 @@
         <v>22</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="K10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="N10" s="23" t="s">
-        <v>87</v>
-      </c>
       <c r="O10" s="20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P10" s="13" t="s">
         <v>53</v>
       </c>
       <c r="Q10" s="19" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R10" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S10" s="17" t="s">
         <v>55</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -1508,37 +1498,37 @@
         <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="K11" s="19" t="s">
         <v>92</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M11" s="23" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N11" s="23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O11" s="20" t="s">
         <v>93</v>
@@ -1550,79 +1540,17 @@
         <v>94</v>
       </c>
       <c r="R11" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S11" s="17" t="s">
         <v>55</v>
       </c>
       <c r="T11" s="16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="L12" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="M12" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="O12" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="R12" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="S12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="T12" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$T$12"/>
+  <autoFilter ref="$A$1:$T$11"/>
   <pageSetup orientation="landscape" paperSize="9"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;P</oddHeader>

--- a/threagile/output/vast/risks.xlsx
+++ b/threagile/output/vast/risks.xlsx
@@ -19,64 +19,64 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
+    <t>Risk Category</t>
+  </si>
+  <si>
+    <t>Technical Asset</t>
+  </si>
+  <si>
+    <t>Communication Link</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Checked by</t>
+  </si>
+  <si>
+    <t>STRIDE</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>RAA %</t>
+  </si>
+  <si>
     <t>Action</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Identified Risk</t>
+  </si>
+  <si>
+    <t>Mitigation</t>
+  </si>
+  <si>
+    <t>Likelihood</t>
+  </si>
+  <si>
+    <t>CWE</t>
+  </si>
+  <si>
     <t>Check</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Checked by</t>
-  </si>
-  <si>
-    <t>Communication Link</t>
-  </si>
-  <si>
-    <t>RAA %</t>
-  </si>
-  <si>
-    <t>Justification</t>
-  </si>
-  <si>
-    <t>STRIDE</t>
-  </si>
-  <si>
-    <t>Likelihood</t>
-  </si>
-  <si>
-    <t>Identified Risk</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>CWE</t>
-  </si>
-  <si>
-    <t>Mitigation</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>Ticket</t>
-  </si>
-  <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Risk Category</t>
-  </si>
-  <si>
-    <t>Technical Asset</t>
   </si>
   <si>
     <t>Elevated</t>
@@ -328,149 +328,127 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="23">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="12"/>
       <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFFF2600"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="12"/>
       <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFA0281E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="12"/>
       <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFFF8E00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="12"/>
       <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFC87832"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="12"/>
       <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF23465F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFFF40FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FFFF9300"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <color rgb="FF008F00"/>
       <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF008F00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -869,64 +847,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="M1" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="Q1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="T1" s="24" t="s">
         <v>19</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="O1" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="S1" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="T1" s="24" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2">
